--- a/products/150-prompt-umkm-premium-premium.xlsx
+++ b/products/150-prompt-umkm-premium-premium.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Library" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Perpustakaan" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Indeks Bab" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Variabel" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Pelacak" state="visible" r:id="rId7"/>
